--- a/data/trans_bre/IP1002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,13</t>
+          <t>-3,74; 1,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,56</t>
+          <t>-2,94; 3,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,4</t>
+          <t>-6,63; -0,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 321,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-66,79; 243,3</t>
+          <t>-68,01; 277,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 15,68</t>
+          <t>-94,4; 28,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 2,24</t>
+          <t>-1,23; 2,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,44</t>
+          <t>-4,38; 0,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 3,78</t>
+          <t>-0,11; 3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,19</t>
+          <t>-3,16; 3,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,54; 898,06</t>
+          <t>-70,11; 586,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,42; 31,78</t>
+          <t>-89,39; 15,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 1044,94</t>
+          <t>-36,03; 1087,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-75,44; 273,52</t>
+          <t>-76,25; 337,62</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,17</t>
+          <t>-0,08; 5,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 0,96</t>
+          <t>-3,7; 1,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,0</t>
+          <t>-2,57; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,93</t>
+          <t>-0,98; 3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 232,84</t>
+          <t>-100,0; 235,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,31</t>
+          <t>-2,59; 0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,78</t>
+          <t>-2,12; 0,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,34</t>
+          <t>-0,89; 1,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; -0,3</t>
+          <t>-3,34; -0,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,12</t>
+          <t>-0,72; 1,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,29</t>
+          <t>-2,17; 0,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,58</t>
+          <t>-1,24; 0,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,12</t>
+          <t>-1,44; 0,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 155,5</t>
+          <t>-46,23; 175,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 21,2</t>
+          <t>-69,25; 19,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,12; 70,29</t>
+          <t>-64,23; 74,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 142,67</t>
+          <t>-65,92; 110,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Edad-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,89</t>
+          <t>-3,64; 2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,58</t>
+          <t>-2,82; 3,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -0,32</t>
+          <t>-7,35; -0,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 321,57</t>
+          <t>-100,0; 563,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,01; 277,53</t>
+          <t>-67,35; 300,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-94,4; 28,14</t>
+          <t>-100,0; 22,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,07</t>
+          <t>-1,22; 2,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,19</t>
+          <t>-4,45; 0,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 3,86</t>
+          <t>-0,18; 3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 3,24</t>
+          <t>-3,21; 3,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,11; 586,39</t>
+          <t>-67,82; 585,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,39; 15,71</t>
+          <t>-86,46; 52,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 1087,34</t>
+          <t>-29,53; 974,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,25; 337,62</t>
+          <t>-74,13; 320,19</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,01</t>
+          <t>-0,16; 5,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 1,05</t>
+          <t>-3,6; 0,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,0</t>
+          <t>-2,59; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,31</t>
+          <t>-0,84; 3,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 235,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,31</t>
+          <t>-2,34; 0,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,78</t>
+          <t>-1,92; 0,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,35</t>
+          <t>-0,88; 1,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -0,28</t>
+          <t>-3,37; -0,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,22</t>
+          <t>-0,81; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,27</t>
+          <t>-2,09; 0,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,64</t>
+          <t>-1,18; 0,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,89</t>
+          <t>-1,17; 1,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-46,23; 175,26</t>
+          <t>-50,99; 175,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 19,17</t>
+          <t>-67,84; 18,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 74,74</t>
+          <t>-63,3; 88,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 110,48</t>
+          <t>-60,81; 137,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,13</t>
+          <t>-3,79; 2,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,61</t>
+          <t>-2,57; 3,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,36</t>
+          <t>-7,18; -0,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 8,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 563,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-67,35; 300,82</t>
+          <t>-66,79; 243,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,38</t>
+          <t>-100,0; 15,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,07</t>
+          <t>-1,25; 2,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,57</t>
+          <t>-4,38; 0,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,86</t>
+          <t>-0,29; 3,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 3,37</t>
+          <t>-2,69; 3,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-67,82; 585,8</t>
+          <t>-71,54; 898,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-86,46; 52,28</t>
+          <t>-86,42; 31,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 974,5</t>
+          <t>-38,62; 1044,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-74,13; 320,19</t>
+          <t>-71,88; 336,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>104,16%</t>
+          <t>105,99%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,08</t>
+          <t>-0,08; 5,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,95</t>
+          <t>-3,33; 0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,0</t>
+          <t>-2,78; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,1</t>
+          <t>-0,78; 3,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 232,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-1,45</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,78</t>
+          <t>-2,11; 0,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,35</t>
+          <t>-0,9; 1,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,28</t>
+          <t>-3,67; -0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>-0,04</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-6,64%</t>
+          <t>-2,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,19</t>
+          <t>-0,76; 1,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,31</t>
+          <t>-2,07; 0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 0,7</t>
+          <t>-1,22; 0,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,01</t>
+          <t>-1,28; 1,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 175,99</t>
+          <t>-50,8; 155,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 18,37</t>
+          <t>-66,55; 21,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-63,3; 88,97</t>
+          <t>-68,12; 70,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,81; 137,71</t>
+          <t>-63,21; 158,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1002-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP1002-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,51</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-28,85%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-72,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-0.6369077302376757</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5110841912522097</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-3.095441609475217</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.508198721091116</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2885187704168726</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.178815249357954</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.7210330374545015</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,162 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 2,13</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-2,57; 3,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,18; -0,4</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-66,79; 243,3</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 15,68</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.788475221998665</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.570754221690554</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.181004350020105</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.6679177549186484</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.130405213547035</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.562365347700296</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-0.4043736069200172</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.598075398172798</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>2.432987685897584</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1568492656045423</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,78%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-55,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>151,06%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,25; 2,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,38; 0,44</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 3,78</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 3,66</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-71,54; 898,06</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-86,42; 31,78</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-38,62; 1044,94</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-71,88; 336,25</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.3997126201695367</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.957864484743358</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.53361352770512</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.4719690982014073</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.3378439989175887</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5507245210522673</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1.510611803807877</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1864891021737581</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>349,23%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-55,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105,99%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.250075415587627</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.381661195735576</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.2932230929023976</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.686378114513271</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.7153600879283396</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.8641661884391724</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3862112050916496</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.7188111124600676</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,08; 5,17</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,33; 0,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,78; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,78; 3,15</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 232,84</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.235553928586837</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.4448990396411833</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.777005920105684</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.663569717778485</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>8.980583429994764</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.3178073461121839</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>10.44944578202749</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>3.362533575823989</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +813,269 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,67</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-67,7%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-27,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.00643425212862</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.158832275500141</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.722727191505227</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.8695624191768999</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>3.492325331096779</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.5551675418710658</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.059917271684271</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,34; 0,31</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 0,78</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 1,34</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; -0,32</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.07722606291809428</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-3.330030646311408</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.784753123702363</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.7834869261812066</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.165600205051506</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9620738155924717</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.152020630092174</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>2.32837150653696</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.66579239637103</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.1461621607029253</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.006317465974304843</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.453981606658465</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.677026980754021</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2734198361151688</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.01439025234060368</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.335338889786488</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.105692561460214</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.897634044571774</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.66556063771122</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.3066509092840357</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.7809766156722353</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.34046737873375</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.3246972165658865</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,23</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,87</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-36,24%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-19,05%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-2,76%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,76; 1,12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,07; 0,29</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,22; 0,58</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 1,19</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-50,8; 155,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-66,55; 21,2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-68,12; 70,29</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-63,21; 158,04</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.2282080865357068</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.8664410971725008</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2577450495145029</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.03898379982820721</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1935507652937852</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.3623918473207454</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1905077030765089</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.0276275359358871</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.7577645490529157</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.068379759669225</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.221460862428278</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.277473350541076</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.5079826704178069</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6654755826905576</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6811564694751115</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.6321262122589971</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.124769700532271</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.2916933617014778</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.5849691601635552</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>1.191293429516993</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.555031496578238</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2119609138976532</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7029281085797116</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.580377024892609</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1083,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
